--- a/data/source/grammar.xlsx
+++ b/data/source/grammar.xlsx
@@ -398,7 +398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y24"/>
+  <dimension ref="A1:Y37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="5" customWidth="1" style="10" min="1" max="1"/>
@@ -3052,19 +3052,1657 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1" s="10"/>
-    <row r="26" ht="15.75" customHeight="1" s="10"/>
-    <row r="27" ht="15.75" customHeight="1" s="10"/>
-    <row r="28" ht="15.75" customHeight="1" s="10"/>
-    <row r="29" ht="15.75" customHeight="1" s="10"/>
-    <row r="30" ht="15.75" customHeight="1" s="10"/>
-    <row r="31" ht="15.75" customHeight="1" s="10"/>
-    <row r="32" ht="15.75" customHeight="1" s="10"/>
-    <row r="33" ht="15.75" customHeight="1" s="10"/>
-    <row r="34" ht="15.75" customHeight="1" s="10"/>
-    <row r="35" ht="15.75" customHeight="1" s="10"/>
-    <row r="36" ht="15.75" customHeight="1" s="10"/>
-    <row r="37" ht="15.75" customHeight="1" s="10"/>
+    <row r="25" ht="15.75" customHeight="1" s="10">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Морфология: глагол</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Будущее время и условное будущее (Ապառնի ժամանակ և ենթադրական ապառնի)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Будущее время образуется так: инфинитив + -ու + вспомогательный глагол: գրելու եմ — «я буду писать, собираюсь писать». Условное будущее — приставка կ- + желательная форма: կգրեմ — «я напишу (наверное, при случае)». Отрицание: չեմ գրելու и չեմ գրի.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Ապառնին կազմվում է այսպես՝ անորոշ դերբայ + -ու + օժանդակ բայ՝ գրելու եմ։ Ենթադրական ապառնին՝ կ- նախածանց + ըղձական ձև՝ կգրեմ։ Ժխտականը՝ չեմ գրելու և չեմ գրի։</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>The future is formed with the infinitive + -ու + the auxiliary: գրելու եմ «I am going to write». The conditional future is կ- + the subjunctive form: կգրեմ «I will (probably) write». Negatives: չեմ գրելու and չեմ գրի.</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1) Будущее время (ապառնի) — это будущее причастие на -ելու/-ալու + եմ, ես, է, ենք, եք, են: խոսելու եմ, կարդալու ես, գնալու է. Оно выражает намерение или запланированное действие: Վաղը Գյումրի եմ գնալու (Завтра я поеду в Гюмри). Порядок в утвердительной форме: причастие + вспомогательный глагол; если в предложении есть выделенное слово, вспомогательный глагол встаёт после него: Վաղը եմ գնալու (Именно завтра поеду). Отрицание: չեմ գնալու, չես գնալու, չի գնալու. 2) Условное будущее (ենթադրական ապառնի): կ- + формы желательного наклонения: կգրեմ, կգրես, կգրի, կգրենք, կգրեք, կգրեն; у глаголов на -ալ — կկարդամ, կկարդաս, կկարդա. Оно выражает предположение, обещание, вежливое согласие: Կզանգեմ (Позвоню), Կգա՞ս (Придёшь?), Անպայման կօգնեմ (Обязательно помогу). Перед гласной կ- пишется слитно: կասեմ, կուտեմ, կանեմ. Отрицание: չեմ + отрицательное причастие: չեմ գրի, չեմ կարդա, չի գա. 3) Будущее в прошедшем: գրելու էի — «я собирался писать»: Զանգելու էի, բայց մոռացա (Я собирался позвонить, но забыл). 4) Разница: գրելու եմ — уверенный план, կգրեմ — обещание или предположение.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>1) Ապառնի ժամանակը կազմվում է ապառնի դերբայով (-ելու/-ալու) և եմ, ես, է, ենք, եք, են օժանդակ բայով՝ խոսելու եմ, կարդալու ես, գնալու է։ Այն արտահայտում է մտադրություն կամ պլանավորված գործողություն՝ Վաղը Գյումրի եմ գնալու։ Եթե նախադասության մեջ կա շեշտված բառ, օժանդակ բայը դրվում է նրանից հետո՝ Վաղը եմ գնալու։ Ժխտականը՝ չեմ գնալու, չես գնալու, չի գնալու։ 2) Ենթադրական ապառնի՝ կ- + ըղձականի ձևեր՝ կգրեմ, կգրես, կգրի, կգրենք, կգրեք, կգրեն, -ալ բայերից՝ կկարդամ, կկարդաս, կկարդա։ Այն արտահայտում է ենթադրություն, խոստում, քաղաքավարի համաձայնություն՝ Կզանգեմ, Կգա՞ս, Անպայման կօգնեմ։ Ձայնավորից առաջ կ-ն գրվում է կից՝ կասեմ, կուտեմ, կանեմ։ Ժխտականը՝ չեմ + ժխտական դերբայ՝ չեմ գրի, չեմ կարդա, չի գա։ 3) Անցյալի ապառնի՝ գրելու էի՝ Զանգելու էի, բայց մոռացա։ 4) Տարբերությունը՝ գրելու եմ՝ վստահ պլան, կգրեմ՝ խոստում կամ ենթադրություն։</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1) The future tense is the future participle in -ելու/-ալու + եմ, ես, է, ենք, եք, են: խոսելու եմ, կարդալու ես, գնալու է. It expresses an intention or a planned action: Վաղը Գյումրի եմ գնալու (Tomorrow I am going to Gyumri). If a word in the sentence is stressed, the auxiliary moves right after it: Վաղը եմ գնալու (It is tomorrow that I am going). Negative: չեմ գնալու, չես գնալու, չի գնալու. 2) The conditional future is կ- + the subjunctive forms: կգրեմ, կգրես, կգրի, կգրենք, կգրեք, կգրեն; for -ալ verbs կկարդամ, կկարդաս, կկարդա. It expresses an assumption, a promise or polite agreement: Կզանգեմ (I will call), Կգա՞ս (Will you come?), Անպայման կօգնեմ (I will definitely help). Before a vowel կ- is written together: կասեմ, կուտեմ, կանեմ. Negative: չեմ + the negative participle: չեմ գրի, չեմ կարդա, չի գա. 3) Future in the past: գրելու էի «I was going to write»: Զանգելու էի, բայց մոռացա (I was going to call but forgot). 4) The difference: գրելու եմ is a firm plan, կգրեմ is a promise or an assumption.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Образуйте будущее время (−ելու եմ) от глаголов: գրել, կարդալ, գնալ, խոսել, սովորել — во всех лицах.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Կազմե՛ք ապառնի ժամանակը (−ելու եմ) գրել, կարդալ, գնալ, խոսել, սովորել բայերից՝ բոլոր դեմքերով։</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Form the future tense (−ելու եմ) of the verbs գրել, կարդալ, գնալ, խոսել, սովորել in all persons.</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Образуйте условное будущее с կ-: ես (զանգել), դու (գալ), նա (ուտել), մենք (անել), նրանք (ասել).</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Կազմե՛ք ենթադրական ապառնին կ-ով՝ ես (զանգել), դու (գալ), նա (ուտել), մենք (անել), նրանք (ասել)։</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Form the conditional future with կ-: ես (զանգել), դու (գալ), նա (ուտել), մենք (անել), նրանք (ասել).</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Переведите: «Завтра я буду работать», «Я тебе позвоню», «Он не придёт», «Мы собирались уехать».</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Թարգմանե՛ք՝ «Завтра я буду работать», «Я тебе позвоню», «Он не придёт», «Мы собирались уехать»։</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Translate: “Tomorrow I am going to work”, “I will call you”, “He won’t come”, “We were going to leave”.</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Поставьте предложения в отрицательную форму: Գնալու եմ։ Կգա։ Կարդալու ենք։ Կասեմ։</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Ժխտական դարձրե՛ք նախադասությունները՝ Գնալու եմ։ Կգա։ Կարդալու ենք։ Կասեմ։</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Make the sentences negative: Գնալու եմ։ Կգա։ Կարդալու ենք։ Կասեմ։</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Напишите 5 предложений о своих планах на выходные, используя −ելու եմ и կ-.</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Գրե՛ք 5 նախադասություն հանգստյան օրերի ձեր պլանների մասին՝ օգտագործելով −ելու եմ և կ- ձևերը։</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Write 5 sentences about your weekend plans using −ելու եմ and կ-.</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>Учебники армянского языка; Armenian: An Essential Grammar (Dum-Tragut); Ժամանակակից հայերենի քերականություն</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1" s="10">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Морфология: глагол</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Желательное наклонение (Ըղձական եղանակ)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Желательное наклонение выражает желание, цель, предложение: գրեմ, գրես, գրի… («чтобы я писал», «давай я напишу»). У глаголов на -ալ: կարդամ, կարդաս, կարդա. Прошедшее желательное: գրեի, կարդայի — «если бы я писал». Часто стоит после որ, որպեսզի, թող, ուզում եմ.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Ըղձական եղանակն արտահայտում է ցանկություն, նպատակ, առաջարկ՝ գրեմ, գրես, գրի։ -ալ բայերից՝ կարդամ, կարդաս, կարդա։ Ըղձական անցյալ՝ գրեի, կարդայի։ Հաճախ գործածվում է որ, որպեսզի, թող, ուզում եմ բառերից հետո։</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>The subjunctive expresses a wish, a purpose or a suggestion: գրեմ, գրես, գրի (“that I write”, “let me write”). For -ալ verbs: կարդամ, կարդաս, կարդա. The past subjunctive: գրեի, կարդայի “if I wrote”. It often follows որ, որպեսզի, թող, ուզում եմ.</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1) Желательное будущее (ըղձական ապառնի): основа + -եմ, -ես, -ի, -ենք, -եք, -են (глаголы на -ել): գրեմ, գրես, գրի, գրենք, գրեք, գրեն; основа + -ամ, -աս, -ա, -անք, -աք, -ան (глаголы на -ալ): կարդամ, կարդաս, կարդա. Неправильные: գալ — գամ, գաս, գա; տալ — տամ, տաս, տա; լինել — լինեմ. 2) Употребление: а) желание: Ուզում եմ գնամ ծով (Хочу поехать на море) — в разговоре после ուզում եմ часто желательная форма вместо инфинитива; б) цель: Եկել եմ, որ օգնեմ (Я пришёл, чтобы помочь), Որպեսզի հասկանաս, կարդա (Чтобы понять, прочитай); в) предложение «давай»: Գնանք (Пойдём), Խոսենք (Поговорим); г) вопрос-совет: Ի՞նչ անեմ (Что мне делать?), Զանգե՞մ (Позвонить?); д) пожелание с թող: Թող գա (Пусть придёт). 3) Прошедшее желательное: -եի, -եիր, -եր, -եինք, -եիք, -եին: գրեի, գրեր; -այի, -այիր, -ար: կարդայի, կարդար. Выражает нереальное желание: Երանի գայիր (Вот бы ты пришёл), и условие: Եթե իմանայի… (Если бы я знал…). 4) Отрицание — приставка չ-: չգրեմ, չկարդա, որ չուշանաս (чтобы ты не опоздал).</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>1) Ըղձական ապառնի՝ հիմք + -եմ, -ես, -ի, -ենք, -եք, -են (-ել բայեր)՝ գրեմ, գրես, գրի, գրենք, գրեք, գրեն, հիմք + -ամ, -աս, -ա, -անք, -աք, -ան (-ալ բայեր)՝ կարդամ, կարդաս, կարդա։ Անկանոններ՝ գալ — գամ, գաս, գա, տալ — տամ, տաս, տա, լինել — լինեմ։ 2) Գործածությունը՝ ա) ցանկություն՝ Ուզում եմ գնամ ծով (խոսակցականում ուզում եմ-ից հետո հաճախ ըղձական է գործածվում), բ) նպատակ՝ Եկել եմ, որ օգնեմ, Որպեսզի հասկանաս, կարդա, գ) առաջարկ՝ Գնանք, Խոսենք, դ) հարց-խորհուրդ՝ Ի՞նչ անեմ, Զանգե՞մ, ե) մաղթանք թող-ով՝ Թող գա։ 3) Ըղձական անցյալ՝ -եի, -եիր, -եր, -եինք, -եիք, -եին՝ գրեի, գրեր, -այի, -այիր, -ար՝ կարդայի, կարդար։ Արտահայտում է անիրական ցանկություն՝ Երանի գայիր, և պայման՝ Եթե իմանայի… 4) Ժխտականը՝ չ- նախածանցով՝ չգրեմ, չկարդա, որ չուշանաս։</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1) Subjunctive future: stem + -եմ, -ես, -ի, -ենք, -եք, -են (-ել verbs): գրեմ, գրես, գրի, գրենք, գրեք, գրեն; stem + -ամ, -աս, -ա, -անք, -աք, -ան (-ալ verbs): կարդամ, կարդաս, կարդա. Irregular: գալ — գամ, գաս, գա; տալ — տամ, տաս, տա; լինել — լինեմ. 2) Uses: a) a wish: Ուզում եմ գնամ ծով (I want to go to the sea) — in speech the subjunctive often replaces the infinitive after ուզում եմ; b) purpose: Եկել եմ, որ օգնեմ (I have come to help), Որպեսզի հասկանաս, կարդա (To understand it, read); c) “let’s”: Գնանք (Let’s go), Խոսենք (Let’s talk); d) asking for advice: Ի՞նչ անեմ (What should I do?), Զանգե՞մ (Shall I call?); e) a wish with թող: Թող գա (Let him come). 3) The past subjunctive: -եի, -եիր, -եր, -եինք, -եիք, -եին: գրեի, գրեր; -այի, -այիր, -ար: կարդայի, կարդար. It expresses an unreal wish: Երանի գայիր (If only you came), and a condition: Եթե իմանայի… (If I knew…). 4) The negative takes չ-: չգրեմ, չկարդա, որ չուշանաս (so that you are not late).</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Проспрягайте в желательном наклонении: խոսել, խաղալ, գալ, տալ.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Խոնարհե՛ք ըղձական եղանակով՝ խոսել, խաղալ, գալ, տալ։</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Conjugate in the subjunctive: խոսել, խաղալ, գալ, տալ.</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Закончите предложения: Եկել եմ, որ… Ուզում եմ… Թող… Ի՞նչ…</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Ավարտե՛ք նախադասությունները՝ Եկել եմ, որ… Ուզում եմ… Թող… Ի՞նչ…</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Complete the sentences: Եկել եմ, որ… Ուզում եմ… Թող… Ի՞նչ…</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Переведите: «Давай пойдём в кино», «Что мне сказать?», «Пусть он позвонит», «Вот бы я знал».</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Թարգմանե՛ք՝ «Давай пойдём в кино», «Что мне сказать?», «Пусть он позвонит», «Вот бы я знал»։</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Translate: “Let’s go to the cinema”, “What should I say?”, “Let him call”, “If only I knew”.</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Поставьте глаголы в прошедшее желательное: ես (իմանալ), դու (գալ), նա (կարդալ), մենք (ունենալ).</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Դրե՛ք բայերը ըղձական անցյալով՝ ես (իմանալ), դու (գալ), նա (կարդալ), մենք (ունենալ)։</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Put the verbs in the past subjunctive: ես (իմանալ), դու (գալ), նա (կարդալ), մենք (ունենալ).</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Напишите 5 пожеланий другу, используя թող и желательное наклонение.</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Գրե՛ք 5 մաղթանք ընկերոջը՝ օգտագործելով թող և ըղձական եղանակը։</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Write 5 wishes to a friend using թող and the subjunctive.</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>Учебники армянского языка; Armenian: An Essential Grammar (Dum-Tragut); Ժամանակակից հայերենի քերականություն</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1" s="10">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Синтаксис</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Условные предложения с եթե (Պայմանական նախադասություններ)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Реальное условие: եթե + желательное / настоящее, затем կ- + будущее: Եթե գաս, կխոսենք (Если придёшь, поговорим). Нереальное условие: եթե + прошедшее желательное, затем կ- + прошедшее желательное: Եթե իմանայի, կասեի (Если бы я знал, я бы сказал).</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Իրական պայման՝ եթե + ըղձական կամ ներկա, ապա կ- + ապառնի՝ Եթե գաս, կխոսենք։ Անիրական պայման՝ եթե + ըղձական անցյալ, ապա կ- + ըղձական անցյալ՝ Եթե իմանայի, կասեի։</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>A real condition: եթե + subjunctive/present, then կ- + future: Եթե գաս, կխոսենք (If you come, we will talk). An unreal condition: եթե + past subjunctive, then կ- + past subjunctive: Եթե իմանայի, կասեի (If I had known, I would have said).</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1) Реальное условие (возможное в будущем): եթե + желательное будущее (գաս, ունենամ) или настоящее время, в главной части — условное будущее с կ- или повелительное: Եթե ժամանակ ունենամ, կզանգեմ (Если будет время, позвоню). Եթե անձրև գա, տանը կմնանք (Если пойдёт дождь, останемся дома). Եթե հոգնել ես, հանգստացիր (Если устал, отдохни). 2) Общее условие (всегда так): եթե + настоящее, главная — настоящее: Եթե ջուրը տաքացնում ես, եռում է (Если нагреваешь воду, она кипит). 3) Нереальное условие (в настоящем или прошлом): եթե + прошедшее желательное (իմանայի, գայիր), главная — условное прошедшее с կ- (կասեի, կգայի): Եթե փող ունենայի, տուն կգնեի (Если бы у меня были деньги, я бы купил дом). Եթե շուտ գայիր, կհանդիպեիր նրան (Если бы ты пришёл раньше, ты бы его встретил). 4) Отрицательное условие: Եթե չգաս, կնեղանամ (Если не придёшь, обижусь); в главной части — չեմ + отрицательное причастие: Եթե իմանայի, չէի ասի (Если бы знал, не сказал бы). 5) Слова-синонимы: որ в разговоре (Որ գաս, կխոսենք), թե (книжное), հակառակ դեպքում (в противном случае).</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>1) Իրական պայման՝ եթե + ըղձական ապառնի (գաս, ունենամ) կամ ներկա, գլխավոր մասում՝ ենթադրական ապառնի կ-ով կամ հրամայական՝ Եթե ժամանակ ունենամ, կզանգեմ։ Եթե անձրև գա, տանը կմնանք։ Եթե հոգնել ես, հանգստացիր։ 2) Ընդհանուր պայման՝ եթե + ներկա, գլխավոր մասում՝ ներկա՝ Եթե ջուրը տաքացնում ես, եռում է։ 3) Անիրական պայման՝ եթե + ըղձական անցյալ (իմանայի, գայիր), գլխավոր մասում՝ ենթադրական անցյալ կ-ով (կասեի, կգայի)՝ Եթե փող ունենայի, տուն կգնեի։ Եթե շուտ գայիր, կհանդիպեիր նրան։ 4) Ժխտական պայման՝ Եթե չգաս, կնեղանամ, գլխավոր մասում՝ չէի + ժխտական դերբայ՝ Եթե իմանայի, չէի ասի։ 5) Հոմանիշներ՝ որ խոսակցականում (Որ գաս, կխոսենք), թե (գրքային), հակառակ դեպքում։</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1) A real condition (possible in the future): եթե + the subjunctive future (գաս, ունենամ) or the present; in the main clause the conditional future with կ- or the imperative: Եթե ժամանակ ունենամ, կզանգեմ (If I have time, I will call). Եթե անձրև գա, տանը կմնանք (If it rains, we will stay at home). Եթե հոգնել ես, հանգստացիր (If you are tired, rest). 2) A general condition: եթե + present, main clause present: Եթե ջուրը տաքացնում ես, եռում է (If you heat water, it boils). 3) An unreal condition: եթե + the past subjunctive (իմանայի, գայիր), main clause the conditional past with կ- (կասեի, կգայի): Եթե փող ունենայի, տուն կգնեի (If I had money, I would buy a house). Եթե շուտ գայիր, կհանդիպեիր նրան (If you had come earlier, you would have met him). 4) A negative condition: Եթե չգաս, կնեղանամ (If you don’t come, I will be hurt); in the main clause չէի + negative participle: Եթե իմանայի, չէի ասի (If I had known, I wouldn’t have said). 5) Synonyms: որ in speech (Որ գաս, կխոսենք), թե (bookish), հակառակ դեպքում (otherwise).</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Соедините части: Եթե անձրև գա… / Եթե փող ունենայի… / Եթե հոգնել ես… — с подходящими продолжениями.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Միացրե՛ք մասերը՝ Եթե անձրև գա… / Եթե փող ունենայի… / Եթե հոգնել ես… — համապատասխան շարունակություններով։</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Match the parts: Եթե անձրև գա… / Եթե փող ունենայի… / Եթե հոգնել ես… with suitable endings.</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Переведите: «Если ты позвонишь, я приду», «Если бы я знал армянский, я бы жил в Ереване».</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Թարգմանե՛ք՝ «Если ты позвонишь, я приду», «Если бы я знал армянский, я бы жил в Ереване»։</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Translate: “If you call, I will come”, “If I knew Armenian, I would live in Yerevan”.</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Превратите реальные условия в нереальные: Եթե գաս, կխոսենք → Եթե գայիր, կխոսեինք (ещё 4 примера).</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Իրական պայմանները դարձրե՛ք անիրական՝ Եթե գաս, կխոսենք → Եթե գայիր, կխոսեինք (ևս 4 օրինակ)։</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Turn real conditions into unreal ones: Եթե գաս, կխոսենք → Եթե գայիր, կխոսեինք (4 more examples).</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Составьте 3 предложения с отрицательным условием (Եթե չ…).</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Կազմե՛ք 3 նախադասություն ժխտական պայմանով (Եթե չ…)։</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Make 3 sentences with a negative condition (Եթե չ…).</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Напишите 5 предложений «Если бы я…» о своей мечте.</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Գրե՛ք 5 նախադասություն «Եթե ես…» ձեր երազանքի մասին։</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Write 5 “If I…” sentences about your dream.</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>Учебники армянского языка; Armenian: An Essential Grammar (Dum-Tragut); Ժամանակակից հայերենի քերականություն</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1" s="10">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Морфология: глагол</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Модальные слова: պետք է, կարող եմ, կարելի է, պիտի (Եղանակավորող բառեր)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Долженствование: պետք է + инфинитив или желательная форма: Պետք է գնալ / Պետք է գնամ (Нужно идти / Я должен идти). Возможность: կարող եմ + инфинитив (Я могу). Разрешение: կարելի է (можно), չի կարելի (нельзя). Пիտի — «должен, предстоит»: Պիտի գամ.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Պարտավորություն՝ պետք է + անորոշ դերբայ կամ ըղձական՝ Պետք է գնալ / Պետք է գնամ։ Հնարավորություն՝ կարող եմ + անորոշ դերբայ։ Թույլտվություն՝ կարելի է, չի կարելի։ Պիտի՝ պարտավորություն կամ ապագա՝ Պիտի գամ։</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Obligation: պետք է + infinitive or subjunctive: Պետք է գնալ / Պետք է գնամ (One must go / I must go). Ability: կարող եմ + infinitive (I can). Permission: կարելի է (it is allowed), չի կարելի (it is not allowed). Պիտի “must, is to”: Պիտի գամ.</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1) Պետք է — «нужно, должен». С инфинитивом — безлично: Պետք է շատ կարդալ (Нужно много читать). С желательной формой — лично: Պետք է գնամ (Я должен идти), Պետք է զանգես (Ты должен позвонить). Отрицание: պետք չէ (не нужно): Պետք չէ անհանգստանալ (Не нужно волноваться). В прошлом: պետք էր գնալ, պետք է գնայի (мне нужно было идти). Также պետք է выражает предположение: Նա պետք է տանը լինի (Он, должно быть, дома). В разговоре: պետք ա. 2) Կարող եմ — «могу»: կարող եմ, կարող ես, կարող է… + инфинитив: Կարող եմ օգնել (Я могу помочь). Отрицание: չեմ կարող գալ. Вопрос-просьба: Կարո՞ղ եք կրկնել (Можете повторить?). Глагол կարողանալ — «суметь»: Կարողացա՞ր (Ты смог?). Разговорно: կարամ, չեմ կարա. 3) Կարելի է — «можно» (разрешение): Կարելի՞ է ներս գալ (Можно войти?). Չի կարելի — «нельзя»: Այստեղ չի կարելի ծխել (Здесь нельзя курить). 4) Պիտի — «должен; предстоит» (сильнее и книжнее): Պիտի հաղթենք (Мы должны победить), а также будущее: Պիտի գամ (Я приду, мне предстоит прийти). 5) Ուզում եմ — «хочу» + инфинитив: Ուզում եմ սովորել (Хочу учиться).</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>1) Պետք է՝ անհրաժեշտություն։ Անորոշ դերբայով՝ անդեմ՝ Պետք է շատ կարդալ։ Ըղձականով՝ դիմավոր՝ Պետք է գնամ, Պետք է զանգես։ Ժխտականը՝ պետք չէ՝ Պետք չէ անհանգստանալ։ Անցյալում՝ պետք էր գնալ, պետք է գնայի։ Պետք է-ն արտահայտում է նաև ենթադրություն՝ Նա պետք է տանը լինի։ Խոսակցականում՝ պետք ա։ 2) Կարող եմ՝ կարող եմ, կարող ես, կարող է… + անորոշ դերբայ՝ Կարող եմ օգնել։ Ժխտականը՝ չեմ կարող գալ։ Հարց-խնդրանք՝ Կարո՞ղ եք կրկնել։ Կարողանալ բայը՝ Կարողացա՞ր։ Խոսակցականում՝ կարամ, չեմ կարա։ 3) Կարելի է՝ թույլտվություն՝ Կարելի՞ է ներս գալ։ Չի կարելի՝ արգելք՝ Այստեղ չի կարելի ծխել։ 4) Պիտի՝ պարտավորություն կամ ապագա (ավելի ուժեղ և գրքային)՝ Պիտի հաղթենք, Պիտի գամ։ 5) Ուզում եմ + անորոշ դերբայ՝ Ուզում եմ սովորել։</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1) Պետք է “it is necessary, must”. With the infinitive it is impersonal: Պետք է շատ կարդալ (One must read a lot). With the subjunctive it is personal: Պետք է գնամ (I must go), Պետք է զանգես (You must call). Negative: պետք չէ (no need): Պետք չէ անհանգստանալ (No need to worry). Past: պետք էր գնալ, պետք է գնայի (I had to go). Պետք է also expresses an assumption: Նա պետք է տանը լինի (He must be at home). In speech: պետք ա. 2) Կարող եմ “I can”: կարող եմ, կարող ես, կարող է… + infinitive: Կարող եմ օգնել (I can help). Negative: չեմ կարող գալ. A polite request: Կարո՞ղ եք կրկնել (Could you repeat?). The verb կարողանալ “to manage”: Կարողացա՞ր (Did you manage?). Colloquially: կարամ, չեմ կարա. 3) Կարելի է “it is allowed”: Կարելի՞ է ներս գալ (May I come in?). Չի կարելի “it is not allowed”: Այստեղ չի կարելի ծխել (No smoking here). 4) Պիտի “must; is to” (stronger, more bookish): Պիտի հաղթենք (We must win), and the future: Պիտի գամ (I am to come). 5) Ուզում եմ “I want” + infinitive: Ուզում եմ սովորել (I want to study).</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Вставьте պետք է, կարող եմ, կարելի է или չի կարելի: Այստեղ … ծխել։ … օգնե՞լ։ Վաղը … շուտ արթնանամ։</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Լրացրե՛ք պետք է, կարող եմ, կարելի է կամ չի կարելի՝ Այստեղ … ծխել։ … օգնե՞լ։ Վաղը … շուտ արթնանամ։</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Fill in պետք է, կարող եմ, կարելի է or չի կարելի: Այստեղ … ծխել։ … օգնե՞լ։ Վաղը … շուտ արթնանամ։</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Переведите: «Мне нужно идти», «Ты можешь помочь?», «Здесь нельзя парковаться», «Он, должно быть, устал».</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Թարգմանե՛ք՝ «Мне нужно идти», «Ты можешь помочь?», «Здесь нельзя парковаться», «Он, должно быть, устал»։</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Translate: “I need to go”, “Can you help?”, “No parking here”, “He must be tired”.</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Составьте 5 правил для гостей вашего дома (Պետք է… / Չի կարելի…).</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Կազմե՛ք 5 կանոն ձեր տան հյուրերի համար (Պետք է… / Չի կարելի…)։</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Write 5 rules for guests in your home (Պետք է… / Չի կարելի…).</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Замените разговорные формы литературными: Կարամ գամ։ Չեմ կարա։ Պետք ա գնանք։</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Խոսակցական ձևերը փոխարինե՛ք գրականով՝ Կարամ գամ։ Չեմ կարա։ Պետք ա գնանք։</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Replace the colloquial forms with literary ones: Կարամ գամ։ Չեմ կարա։ Պետք ա գնանք։</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Напишите, что вы должны, можете и хотите сделать на этой неделе (по 2 предложения).</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Գրե՛ք, թե ինչ պետք է, կարող եք և ուզում եք անել այս շաբաթ (2-ական նախադասություն)։</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Write what you must, can and want to do this week (2 sentences each).</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>Учебники армянского языка; Armenian: An Essential Grammar (Dum-Tragut); Ժամանակակից հայերենի քերականություն</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1" s="10">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Морфология: глагол</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Причастия: −ած, −ող, −ելիս, −ելով (Դերբայներ)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Причастие результата на -ած: գրած նամակ (написанное письмо), եկած հյուր (приехавший гость). Причастие деятеля на -ող: խոսող մարդ (говорящий человек), ուսանող (студент). Деепричастие на -ելիս: Տուն գալիս (Приходя домой). На -ելով: Կարդալով սովորում ենք (Учимся, читая).</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Հարակատար դերբայ (-ած)՝ գրած նամակ, եկած հյուր։ Ենթակայական դերբայ (-ող)՝ խոսող մարդ, ուսանող։ Համակատար դերբայ (-ելիս)՝ Տուն գալիս։ Միջոցի ձև (-ելով)՝ Կարդալով սովորում ենք։</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>The resultative participle in -ած: գրած նամակ (a written letter), եկած հյուր (a guest who has arrived). The agent participle in -ող: խոսող մարդ (a speaking person), ուսանող (student). The converb in -ելիս: Տուն գալիս (When coming home). With -ելով: Կարդալով սովորում ենք (We learn by reading).</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1) Причастие на -ած (հարակատար) — завершённое действие, результат. Образуется от перфективной основы: գրել → գրած, կարդալ → կարդացած, տեսնել → տեսած, գալ → եկած, ուտել → կերած, անել → արած. Употребляется как определение: Կարդացած գիրքը (Прочитанная книга), Ուշացած գնացքը (Опоздавший поезд); и в составе времени: Նա հոգնած է (Он устал). 2) Причастие на -ող (ենթակայական) — тот, кто делает: գրող (пишущий; писатель), վարող (водитель), խոսող, կարդացող. Многие такие причастия стали существительными: ուսանող (студент), դասավանդող (преподаватель), աշխատող (работник). 3) На -ելիս/-ալիս (համակատար) — «когда делаешь»: Ճաշելիս չեն խոսում (Во время еды не разговаривают), Փողոցն անցնելիս զգույշ եղիր (Переходя улицу, будь осторожен). 4) На -ելով/-ալով — способ действия: Ժպտալով ասաց (Сказал, улыбаясь), Աշխատելով ենք հասնում (Добиваемся, трудясь). 5) Прочие причастия (уже встречались): -ում (գրում եմ), -ել (գրել եմ), -ելու (գրելու եմ), отрицательное -ի/-ա (չեմ գրի). 6) С отрицанием -ած/-ող пишутся с չ-: չկարդացած, չաշխատող.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>1) Հարակատար դերբայ (-ած)՝ ավարտված գործողություն, արդյունք։ Կազմվում է վաղակատար հիմքից՝ գրել → գրած, կարդալ → կարդացած, տեսնել → տեսած, գալ → եկած, ուտել → կերած, անել → արած։ Գործածվում է որպես որոշիչ՝ Կարդացած գիրքը, Ուշացած գնացքը, և ժամանակաձևերում՝ Նա հոգնած է։ 2) Ենթակայական դերբայ (-ող)՝ գործողություն կատարողը՝ գրող, վարող, խոսող, կարդացող։ Շատերը դարձել են գոյականներ՝ ուսանող, դասավանդող, աշխատող։ 3) Համակատար դերբայ (-ելիս/-ալիս)՝ Ճաշելիս չեն խոսում, Փողոցն անցնելիս զգույշ եղիր։ 4) -ելով/-ալով ձևը՝ գործողության եղանակ՝ Ժպտալով ասաց, Աշխատելով ենք հասնում։ 5) Այլ դերբայներ՝ -ում (գրում եմ), -ել (գրել եմ), -ելու (գրելու եմ), ժխտական -ի/-ա (չեմ գրի)։ 6) Ժխտականով -ած/-ող ձևերը գրվում են չ-ով՝ չկարդացած, չաշխատող։</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1) The participle in -ած (resultative) shows a completed action, a result. It is formed from the perfective stem: գրել → գրած, կարդալ → կարդացած, տեսնել → տեսած, գալ → եկած, ուտել → կերած, անել → արած. It is used as an attribute: Կարդացած գիրքը (The book that has been read), Ուշացած գնացքը (The late train); and in tense forms: Նա հոգնած է (He is tired). 2) The participle in -ող (agent) means the one who does: գրող (writing; writer), վարող (driver), խոսող, կարդացող. Many have become nouns: ուսանող (student), դասավանդող (teacher), աշխատող (worker). 3) -ելիս/-ալիս means “while doing”: Ճաշելիս չեն խոսում (People don’t talk while eating), Փողոցն անցնելիս զգույշ եղիր (Be careful when crossing the street). 4) -ելով/-ալով shows the manner: Ժպտալով ասաց (He said smiling), Աշխատելով ենք հասնում (We achieve it by working). 5) Other participles you have met: -ում (գրում եմ), -ել (գրել եմ), -ելու (գրելու եմ), the negative -ի/-ա (չեմ գրի). 6) With negation, -ած/-ող forms take չ-: չկարդացած, չաշխատող.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Образуйте причастия на -ած и -ող: գրել, կարդալ, տեսնել, գալ, ուտել, աշխատել.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Կազմե՛ք -ած և -ող դերբայներ՝ գրել, կարդալ, տեսնել, գալ, ուտել, աշխատել։</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Form the -ած and -ող participles of գրել, կարդալ, տեսնել, գալ, ուտել, աշխատել.</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Переведите: «прочитанная книга», «пришедший гость», «говорящий человек», «во время еды».</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Թարգմանե՛ք՝ «прочитанная книга», «пришедший гость», «говорящий человек», «во время еды»։</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Translate: “a book that has been read”, “a guest who has arrived”, “a speaking person”, “while eating”.</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Замените придаточные причастиями: Գիրքը, որը կարդացել եմ… → Կարդացածս գիրքը…</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Ստորադասականները փոխարինե՛ք դերբայներով՝ Գիրքը, որը կարդացել եմ… → Կարդացածս գիրքը…</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Replace the clauses with participles: Գիրքը, որը կարդացել եմ… → Կարդացածս գիրքը…</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Составьте 4 предложения с -ելիս (что вы делаете, когда…).</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Կազմե՛ք 4 նախադասություն -ելիս ձևով (ինչ եք անում, երբ…)։</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Make 4 sentences with -ելիս (what you do when…).</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Найдите в словаре 5 существительных, образованных от причастий на -ող.</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Բառարանում գտե՛ք -ող դերբայից կազմված 5 գոյական։</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Find 5 nouns formed from -ող participles in the dictionary.</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>Учебники армянского языка; Armenian: An Essential Grammar (Dum-Tragut); Ժամանակակից հայերենի քերականություն</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1" s="10">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Морфология: глагол</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Страдательный и побудительный залог: −վ−, −ցն− (Կրավորական և պատճառական բայեր)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Страдательный залог: суффикс -վ-: գրել → գրվել (писаться, быть написанным): Նամակը գրվեց (Письмо было написано). Побудительный (каузатив): суффикс -ցն-/-եցն-: նստել → նստեցնել (усадить), ուրախանալ → ուրախացնել (обрадовать).</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Կրավորական սեռ՝ -վ- ածանց՝ գրել → գրվել՝ Նամակը գրվեց։ Պատճառական սեռ՝ -ցն-/-եցն- ածանց՝ նստել → նստեցնել, ուրախանալ → ուրախացնել։</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>The passive uses the suffix -վ-: գրել → գրվել (to be written): Նամակը գրվեց (The letter was written). The causative uses -ցն-/-եցն-: նստել → նստեցնել (to seat someone), ուրախանալ → ուրախացնել (to make happy).</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1) Страдательный залог (կրավորական սեռ): к основе добавляется -վ-, глагол спрягается как обычный глагол на -ել: գրել → գրվել, կառուցել → կառուցվել, բացել → բացվել, ուտել → ուտվել. Пример: Տունը կառուցվել է 1960 թվականին (Дом был построен в 1960 году). Исполнитель действия — с послелогом կողմից: Գիրքը գրվել է հայտնի գրողի կողմից (Книга написана известным писателем). Многие глаголы на -վել — возвратные или самостоятельные: լվացվել (умываться), հագնվել (одеваться). 2) Побудительный залог (պատճառական): -ցն- или -եցն- (глаголы на -ել), -ացն- (глаголы на -անալ/-ալ): նստել → նստեցնել (усадить), խմել → խմեցնել (напоить), ուրախանալ → ուրախացնել (обрадовать), վախենալ → վախեցնել (напугать), հասկանալ → հասկացնել (объяснить, дать понять), զարմանալ → զարմացնել (удивить). Аорист каузативов: -ցրի, -ցրիր, -ցրեց: Նա ինձ զարմացրեց (Он меня удивил). Повелительное: -ցրու, -ցրեք: Նստեցրու երեխային (Усади ребёнка). 3) Пары «состояние — причина»: տաքանալ (нагреваться) — տաքացնել (нагревать); սառչել (мёрзнуть) — սառեցնել (замораживать); վերջանալ (заканчиваться) — վերջացնել (заканчивать).</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>1) Կրավորական սեռ՝ հիմքին ավելանում է -վ-, և բայը խոնարհվում է որպես -ել բայ՝ գրել → գրվել, կառուցել → կառուցվել, բացել → բացվել։ Օրինակ՝ Տունը կառուցվել է 1960 թվականին։ Գործողություն կատարողը՝ կողմից կապով՝ Գիրքը գրվել է հայտնի գրողի կողմից։ -վել բայերի մի մասը անդրադարձ կամ ինքնուրույն է՝ լվացվել, հագնվել։ 2) Պատճառական սեռ՝ -ցն- կամ -եցն- (-ել բայեր), -ացն- (-անալ/-ալ բայեր)՝ նստել → նստեցնել, խմել → խմեցնել, ուրախանալ → ուրախացնել, վախենալ → վախեցնել, հասկանալ → հասկացնել, զարմանալ → զարմացնել։ Պատճառական բայերի անցյալ կատարյալը՝ -ցրի, -ցրիր, -ցրեց՝ Նա ինձ զարմացրեց։ Հրամայականը՝ -ցրու, -ցրեք՝ Նստեցրու երեխային։ 3) «Վիճակ — պատճառ» զույգեր՝ տաքանալ — տաքացնել, սառչել — սառեցնել, վերջանալ — վերջացնել։</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1) The passive: -վ- is added to the stem and the verb is conjugated like an -ել verb: գրել → գրվել, կառուցել → կառուցվել, բացել → բացվել. Example: Տունը կառուցվել է 1960 թվականին (The house was built in 1960). The agent is expressed with the postposition կողմից: Գիրքը գրվել է հայտնի գրողի կողմից (The book was written by a famous writer). Some -վել verbs are reflexive or independent: լվացվել (to wash oneself), հագնվել (to get dressed). 2) The causative: -ցն- or -եցն- (-ել verbs), -ացն- (-անալ/-ալ verbs): նստել → նստեցնել (to seat), խմել → խմեցնել (to give a drink), ուրախանալ → ուրախացնել (to make happy), վախենալ → վախեցնել (to frighten), հասկանալ → հասկացնել (to make understand), զարմանալ → զարմացնել (to surprise). Causatives in the aorist: -ցրի, -ցրիր, -ցրեց: Նա ինձ զարմացրեց (He surprised me). Imperative: -ցրու, -ցրեք: Նստեցրու երեխային (Seat the child). 3) “State — cause” pairs: տաքանալ (to get warm) — տաքացնել (to heat); սառչել (to freeze) — սառեցնել (to freeze something); վերջանալ (to end) — վերջացնել (to finish).</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Образуйте страдательные глаголы: գրել, բացել, կառուցել, ուղարկել, վաճառել.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Կազմե՛ք կրավորական բայեր՝ գրել, բացել, կառուցել, ուղարկել, վաճառել։</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Form passive verbs from գրել, բացել, կառուցել, ուղարկել, վաճառել.</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Образуйте побудительные глаголы: նստել, ուրախանալ, վախենալ, զարմանալ, տաքանալ.</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Կազմե՛ք պատճառական բայեր՝ նստել, ուրախանալ, վախենալ, զարմանալ, տաքանալ։</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Form causative verbs from նստել, ուրախանալ, վախենալ, զարմանալ, տաքանալ.</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Переделайте в страдательный залог: Վարպետը կառուցեց տունը։ Մայրը լվաց սպասքը։</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Դարձրե՛ք կրավորական՝ Վարպետը կառուցեց տունը։ Մայրը լվաց սպասքը։</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Make passive: Վարպետը կառուցեց տունը։ Մայրը լվաց սպասքը։</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Переведите: «Магазин открывается в девять», «Новость меня обрадовала», «Нагрей воду».</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Թարգմանե՛ք՝ «Магазин открывается в девять», «Новость меня обрадовала», «Нагрей воду»։</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Translate: “The shop opens at nine”, “The news made me happy”, “Heat the water”.</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Составьте 3 пары предложений «состояние — причина» (ուրախացա — ուրախացրեց).</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Կազմե՛ք 3 զույգ նախադասություն «վիճակ — պատճառ» (ուրախացա — ուրախացրեց)։</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Make 3 pairs of “state — cause” sentences (ուրախացա — ուրախացրեց).</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>Учебники армянского языка; Armenian: An Essential Grammar (Dum-Tragut); Ժամանակակից հայերենի քերականություն</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1" s="10">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Морфология: имя</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Послелоги: մեջ, վրա, տակ, մոտ, հետ, համար, մասին (Կապեր)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>В армянском вместо предлогов — послелоги: они стоят после слова в родительном падеже. Սեղանի վրա (на столе), տան մեջ (в доме), աթոռի տակ (под стулом), ընկերոջ հետ (с другом), քեզ համար (для тебя), Հայաստանի մասին (об Армении).</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Հայերենում նախդիրների փոխարեն կապեր են, որոնք դրվում են սեռական հոլովով բառից հետո՝ սեղանի վրա, տան մեջ, աթոռի տակ, ընկերոջ հետ, քեզ համար, Հայաստանի մասին։</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Instead of prepositions Armenian uses postpositions placed after a word in the genitive: սեղանի վրա (on the table), տան մեջ (in the house), աթոռի տակ (under the chair), ընկերոջ հետ (with a friend), քեզ համար (for you), Հայաստանի մասին (about Armenia).</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1) Послелоги ставятся ПОСЛЕ существительного, обычно в родительном падеже (с определённым артиклем часто без него): սեղանի վրա (на столе), պատի վրա (на стене), դռան մոտ (у двери), տան առաջ (перед домом), տան հետևում (за домом), աթոռի տակ (под стулом), դպրոցի կողքին (рядом со школой), քաղաքի կենտրոնում (в центре города). 2) Направление и место: վրա — на; մեջ — в, внутри (Արկղի մեջ — в коробке; часто заменяется местным падежом: արկղում); տակ — под; մոտ — у, около; также «у кого-то дома»: Տատիկիս մոտ եմ (Я у бабушки); առաջ — перед (и «раньше»: ժամից առաջ); հետո — после (դասից հետո). 3) Отношения: հետ — с (Ընկերոջս հետ եմ գնում — Иду с другом); համար — для, из-за (Քեզ համար է — Это для тебя); մասին — о (Խոսենք Երևանի մասին — Поговорим о Ереване); փոխարեն — вместо (Թեյի փոխարեն սուրճ — Кофе вместо чая); դեմ — против (Ես դեմ եմ — Я против); շնորհիվ — благодаря; պատճառով — из-за (Անձրևի պատճառով չեկանք — Из-за дождя мы не пришли); կողմից — со стороны, кем (в страдательном). 4) С местоимениями: ինձ հետ (со мной), քեզ համար (для тебя), նրա մասին (о нём), մեզ մոտ (у нас). 5) Некоторые послелоги требуют других падежей: մինչև + именительный/дательный (մինչև վաղը — до завтра), դեպի + именительный (դեպի ծով — к морю, это предлог!), առանց + родительный (առանց շաքարի — без сахара, тоже предлог).</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>1) Կապերը դրվում են գոյականից ՀԵՏՈ, սովորաբար սեռական հոլովով՝ սեղանի վրա, պատի վրա, դռան մոտ, տան առաջ, տան հետևում, աթոռի տակ, դպրոցի կողքին, քաղաքի կենտրոնում։ 2) Տեղ և ուղղություն՝ վրա, մեջ (Արկղի մեջ, հաճախ փոխարինվում է ներգոյականով՝ արկղում), տակ, մոտ (նաև «ինչ-որ մեկի տանը»՝ Տատիկիս մոտ եմ), առաջ (նաև ժամանակ՝ ժամից առաջ), հետո (դասից հետո)։ 3) Հարաբերություններ՝ հետ (Ընկերոջս հետ եմ գնում), համար (Քեզ համար է), մասին (Խոսենք Երևանի մասին), փոխարեն (Թեյի փոխարեն սուրճ), դեմ (Ես դեմ եմ), շնորհիվ, պատճառով (Անձրևի պատճառով չեկանք), կողմից։ 4) Դերանուններով՝ ինձ հետ, քեզ համար, նրա մասին, մեզ մոտ։ 5) Որոշ կապեր այլ հոլով են պահանջում՝ մինչև (մինչև վաղը), դեպի (դեպի ծով, նախդիր է), առանց + սեռական (առանց շաքարի, նույնպես նախդիր)։</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1) Postpositions come AFTER the noun, usually in the genitive: սեղանի վրա (on the table), պատի վրա (on the wall), դռան մոտ (by the door), տան առաջ (in front of the house), տան հետևում (behind the house), աթոռի տակ (under the chair), դպրոցի կողքին (next to the school), քաղաքի կենտրոնում (in the city centre). 2) Place and direction: վրա — on; մեջ — in, inside (Արկղի մեջ — in the box; often replaced by the locative: արկղում); տակ — under; մոտ — near, by; also “at someone’s place”: Տատիկիս մոտ եմ (I am at my grandmother’s); առաջ — in front of (and “before”: ժամից առաջ); հետո — after (դասից հետո). 3) Relations: հետ — with (Ընկերոջս հետ եմ գնում — I am going with my friend); համար — for, because of (Քեզ համար է — It is for you); մասին — about (Խոսենք Երևանի մասին — Let’s talk about Yerevan); փոխարեն — instead of (Թեյի փոխարեն սուրճ — Coffee instead of tea); դեմ — against (Ես դեմ եմ — I am against); շնորհիվ — thanks to; պատճառով — because of (Անձրևի պատճառով չեկանք — We didn’t come because of the rain); կողմից — by (in the passive). 4) With pronouns: ինձ հետ (with me), քեզ համար (for you), նրա մասին (about him), մեզ մոտ (at our place). 5) Some take other cases: մինչև + nominative/dative (մինչև վաղը — until tomorrow), դեպի + nominative (դեպի ծով — towards the sea, a preposition!), առանց + genitive (առանց շաքարի — without sugar, also a preposition).</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Опишите свою комнату: что где лежит (5 предложений с վրա, տակ, մոտ, մեջ, կողքին).</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Նկարագրե՛ք ձեր սենյակը՝ ինչն որտեղ է (5 նախադասություն վրա, տակ, մոտ, մեջ, կողքին կապերով)։</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Describe your room: where things are (5 sentences with վրա, տակ, մոտ, մեջ, կողքին).</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Вставьте послелог: Գիրքը սեղանի … է։ Գնում եմ ընկերոջս …։ Սա քեզ … է։ Խոսում ենք ֆիլմի …։</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Լրացրե՛ք կապը՝ Գիրքը սեղանի … է։ Գնում եմ ընկերոջս …։ Սա քեզ … է։ Խոսում ենք ֆիլմի …։</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Fill in the postposition: Գիրքը սեղանի … է։ Գնում եմ ընկերոջս …։ Սա քեզ … է։ Խոսում ենք ֆիլմի …։</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Переведите: «после урока», «перед домом», «из-за погоды», «вместо меня», «без сахара».</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Թարգմանե՛ք՝ «после урока», «перед домом», «из-за погоды», «вместо меня», «без сахара»։</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Translate: “after the lesson”, “in front of the house”, “because of the weather”, “instead of me”, “without sugar”.</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Поставьте слова в нужный падеж перед послелогом: (տուն) մոտ, (ընկեր) հետ, (Երևան) մասին.</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Դրե՛ք բառերը ճիշտ հոլովով կապից առաջ՝ (տուն) մոտ, (ընկեր) հետ, (Երևան) մասին։</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Put the words in the right case before the postposition: (տուն) մոտ, (ընկեր) հետ, (Երևան) մասին.</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Расскажите, с кем, для кого и о чём вы говорили вчера (4 предложения).</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Պատմե՛ք, թե երեկ ում հետ, ում համար և ինչի մասին եք խոսել (4 նախադասություն)։</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Tell whom you talked with, for whom and about what yesterday (4 sentences).</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>Учебники армянского языка; Armenian: An Essential Grammar (Dum-Tragut); Ժամանակակից հայերենի քերականություն</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1" s="10">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Синтаксис</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Придаточные предложения: որ, որը, ով, երբ, որտեղ (Ստորադասական նախադասություններ)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Որ — универсальный союз «что, чтобы, который»: Գիտեմ, որ գալու ես (Знаю, что ты придёшь). Относительные: որը (который — о предметах), ով (кто — о людях), երբ (когда), որտեղ (где): Այն տունը, որտեղ ապրում եմ… (Дом, где я живу…).</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Որ՝ համընդհանուր շաղկապ՝ Գիտեմ, որ գալու ես։ Հարաբերականներ՝ որը (առարկաների մասին), ով (մարդկանց մասին), երբ, որտեղ՝ Այն տունը, որտեղ ապրում եմ…</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Որ is a universal conjunction “that, so that, which”: Գիտեմ, որ գալու ես (I know that you will come). Relative words: որը (which — for things), ով (who — for people), երբ (when), որտեղ (where): Այն տունը, որտեղ ապրում եմ… (The house where I live…).</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1) Изъяснительные (что?): главная + որ: Ասաց, որ կուշանա (Сказал, что опоздает). Կարծում եմ, որ ճիշտ ես (Думаю, что ты прав). 2) Цели (чтобы): որ / որպեսզի + желательное: Եկա, որ տեսնեմ քեզ (Пришёл, чтобы увидеть тебя). Որպեսզի չուշանաս, շուտ դուրս արի (Чтобы не опоздать, выходи пораньше). 3) Определительные (который): а) որ — самый частый, неизменяемый: Այն գիրքը, որ տվեցիր, հետաքրքիր է (Книга, которую ты дал, интересная); б) որը, որի, որին, որից, որով, որում — склоняется (о предметах и людях): Մարդը, որի հետ խոսում էի, բժիշկ է (Человек, с которым я говорил, врач); в) ով, ում, ումից — о людях: Նա, ով շատ է կարդում, շատ գիտի (Тот, кто много читает, много знает). 4) Времени: երբ (когда), մինչև (пока), հենց որ (как только): Երբ գաս, կզանգես (Когда придёшь, позвони). Հենց որ վերջացնեմ, կգամ (Как только закончу, приду). 5) Места: որտեղ (где), ուր (куда): Գնացինք այնտեղ, որտեղ ծնվել էր (Мы поехали туда, где он родился). 6) Причины: որովհետև, քանի որ (потому что, так как): Չեկա, քանի որ հիվանդ էի (Не пришёл, так как был болен). 7) В армянском придаточное часто стоит перед главным, а запятая ставится всегда.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>1) Լրացական (ի՞նչ)՝ գլխավոր + որ՝ Ասաց, որ կուշանա։ Կարծում եմ, որ ճիշտ ես։ 2) Նպատակի՝ որ / որպեսզի + ըղձական՝ Եկա, որ տեսնեմ քեզ։ Որպեսզի չուշանաս, շուտ դուրս արի։ 3) Որոշիչ՝ ա) որ՝ ամենահաճախը, անփոփոխ՝ Այն գիրքը, որ տվեցիր, հետաքրքիր է, բ) որը, որի, որին, որից, որով, որում՝ հոլովվում է՝ Մարդը, որի հետ խոսում էի, բժիշկ է, գ) ով, ում, ումից՝ մարդկանց մասին՝ Նա, ով շատ է կարդում, շատ գիտի։ 4) Ժամանակի՝ երբ, մինչև, հենց որ՝ Երբ գաս, կզանգես։ Հենց որ վերջացնեմ, կգամ։ 5) Տեղի՝ որտեղ, ուր՝ Գնացինք այնտեղ, որտեղ ծնվել էր։ 6) Պատճառի՝ որովհետև, քանի որ՝ Չեկա, քանի որ հիվանդ էի։ 7) Հայերենում ստորադասականը հաճախ գլխավորից առաջ է, իսկ ստորակետը դրվում է միշտ։</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1) Object clauses (what?): main clause + որ: Ասաց, որ կուշանա (He said he would be late). Կարծում եմ, որ ճիշտ ես (I think you are right). 2) Purpose (so that): որ / որպեսզի + subjunctive: Եկա, որ տեսնեմ քեզ (I came to see you). Որպեսզի չուշանաս, շուտ դուրս արի (Leave early so as not to be late). 3) Relative clauses (which/who): a) որ — the most frequent, unchangeable: Այն գիրքը, որ տվեցիր, հետաքրքիր է (The book you gave me is interesting); b) որը, որի, որին, որից, որով, որում — declined (things and people): Մարդը, որի հետ խոսում էի, բժիշկ է (The man I was talking to is a doctor); c) ով, ում, ումից — for people: Նա, ով շատ է կարդում, շատ գիտի (He who reads a lot knows a lot). 4) Time: երբ (when), մինչև (until), հենց որ (as soon as): Երբ գաս, կզանգես (When you come, call). Հենց որ վերջացնեմ, կգամ (As soon as I finish, I will come). 5) Place: որտեղ (where), ուր (where to): Գնացինք այնտեղ, որտեղ ծնվել էր (We went where he had been born). 6) Reason: որովհետև, քանի որ (because, since): Չեկա, քանի որ հիվանդ էի (I didn’t come since I was ill). 7) In Armenian the subordinate clause often comes before the main one, and a comma is always used.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Соедините предложения с помощью որ: Գիտեմ։ Նա կգա։ / Ասաց։ Հոգնել է։</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Միացրե՛ք նախադասությունները որ-ով՝ Գիտեմ։ Նա կգա։ / Ասաց։ Հոգնել է։</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Join the sentences with որ: Գիտեմ։ Նա կգա։ / Ասաց։ Հոգնել է։</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Вставьте որը, ով, որտեղ, երբ: Քաղաքը, … ծնվել եմ… / Մարդը, … զանգեց… / … գաս, կխոսենք։</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Լրացրե՛ք որը, ով, որտեղ, երբ՝ Քաղաքը, … ծնվել եմ… / Մարդը, … զանգեց… / … գաս, կխոսենք։</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Fill in որը, ով, որտեղ, երբ: Քաղաքը, … ծնվել եմ… / Մարդը, … զանգեց… / … գաս, կխոսենք։</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Переведите: «Я знаю, что ты занят», «Я пришёл, чтобы помочь», «Город, где я живу, красивый».</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Թարգմանե՛ք՝ «Я знаю, что ты занят», «Я пришёл, чтобы помочь», «Город, где я живу, красивый»։</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Translate: “I know you are busy”, “I came to help”, “The city where I live is beautiful”.</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Составьте 3 предложения с причиной (որովհետև, քանի որ).</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Կազմե՛ք պատճառի 3 նախադասություն (որովհետև, քանի որ)։</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Make 3 sentences of reason (որովհետև, քանի որ).</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Опишите человека, которого вы уважаете, используя որը/ով/որ (5 предложений).</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Նկարագրե՛ք մի մարդու, որին հարգում եք՝ օգտագործելով որը/ով/որ (5 նախադասություն)։</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Describe a person you respect using որը/ով/որ (5 sentences).</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>Учебники армянского языка; Armenian: An Essential Grammar (Dum-Tragut); Ժամանակակից հայերենի քերականություն</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="15.75" customHeight="1" s="10">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Живой язык</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Разговорная речь Еревана (Երևանյան խոսակցական լեզու)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>В разговоре армяне говорят не так, как пишут: «ա» вместо «է» (գնում ա), կարամ вместо կարող եմ, ո՞նց вместо ինչպե՞ս, էս/էդ/էն вместо այս/այդ/այն, էգուց вместо վաղը, повелительное на -ի (նայի, սպասի). Это норма живой речи, но в письме и официально — литературные формы.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Խոսակցական լեզուն տարբերվում է գրականից՝ «ա» «է»-ի փոխարեն (գնում ա), կարամ՝ կարող եմ-ի փոխարեն, ո՞նց՝ ինչպե՞ս-ի, էս/էդ/էն՝ այս/այդ/այն-ի, էգուց՝ վաղը-ի փոխարեն, հրամայական -ի-ով (նայի, սպասի)։ Գրավոր և պաշտոնական խոսքում՝ գրական ձևեր։</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Armenians speak differently from how they write: «ա» instead of «է» (գնում ա), կարամ instead of կարող եմ, ո՞նց instead of ինչպե՞ս, էս/էդ/էն instead of այս/այդ/այն, էգուց instead of վաղը, the imperative in -ի (նայի, սպասի). This is normal in speech, but writing and official speech use literary forms.</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1) Связка и вспомогательный глагол 3 лица: «ա» вместо «է»: Ի՞նչ ա (Что такое?), Լավ ա (Хорошо), Գնում ա (Он идёт), Եկել ա (Пришёл), Պետք ա (Надо). В отрицании «չի» остаётся: Չի գալիս. 2) Указательные слова: էս (этот), էդ (тот, возле тебя), էն (тот), էստեղ, էդտեղ, էնտեղ (здесь, там), էսպես, էդպես/տենց (так), էսքան, էդքան (столько), էսօր (сегодня). 3) Вопросы: ո՞նց (как), ինչի՞ (почему), ինչքա՞ն (сколько), ու՞ր (куда), ո՞վ ա (кто это). 4) Глагол «мочь»: կարամ, կարաս, կարա, կարանք, կարաք, կարան; չեմ կարա (не могу). 5) Повелительное наклонение глаголов на -ել: -ի вместо -իր: նայի, սպասի, գրի, զանգի, խմի, լսի; տու вместо տուր. 6) Разговорный аорист: ասի, ասեց (вместо ասացի, ասաց), տվի (вместо տվեցի). 7) Слова: էգուց (завтра), էրեկ (вчера), ձեն (голос), փող (деньги), գործ (работа), սաղ (все), մենակ (только), լրիվ (совсем), մի հատ (чуть-чуть, «-ка»). 8) Частицы: էլի (ну пожалуйста), դե (ну), բա (а), հը (ну?), ախր (ведь), հո (же). 9) Заимствования из русского: մերսի (из французского), նորմալ, պրոբլեմ, մարշրուտկա, պրոբկա, վաբշե. 10) Где что уместно: с друзьями, в такси, на рынке — разговорные формы звучат естественно; в документах, письмах, на экзамене — только литературные. В приложении разговорные слова отмечены «разг.»; в настройках можно включить «Сначала разговорные формы».</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>1) Օժանդակ բայի 3-րդ դեմք՝ «ա» «է»-ի փոխարեն՝ Ի՞նչ ա, Լավ ա, Գնում ա, Եկել ա, Պետք ա։ Ժխտականում «չի»-ն մնում է՝ Չի գալիս։ 2) Ցուցական բառեր՝ էս, էդ, էն, էստեղ, էդտեղ, էնտեղ, էսպես, էդպես/տենց, էսքան, էդքան, էսօր։ 3) Հարցեր՝ ո՞նց, ինչի՞, ինչքա՞ն, ու՞ր, ո՞վ ա։ 4) Կարողանալ բայը՝ կարամ, կարաս, կարա, կարանք, կարաք, կարան, չեմ կարա։ 5) -ել բայերի հրամայականը՝ -ի -իր-ի փոխարեն՝ նայի, սպասի, գրի, զանգի, խմի, լսի, տու՝ տուր-ի փոխարեն։ 6) Խոսակցական անցյալ կատարյալ՝ ասի, ասեց (ասացի, ասաց), տվի (տվեցի)։ 7) Բառեր՝ էգուց, էրեկ, ձեն, փող, գործ, սաղ, մենակ, լրիվ, մի հատ։ 8) Մասնիկներ՝ էլի, դե, բա, հը, ախր, հո։ 9) Փոխառություններ ռուսերենից՝ մերսի (ֆրանսերենից), նորմալ, պրոբլեմ, մարշրուտկա, պրոբկա, վաբշե։ 10) Ինչն որտեղ է տեղին՝ ընկերների հետ, տաքսիում, շուկայում խոսակցական ձևերը բնական են, փաստաթղթերում, նամակներում, քննությանը՝ միայն գրական։ Հավելվածում խոսակցական բառերը նշված են «խսկց.», իսկ կարգավորումներում կարելի է միացնել «Սկզբում խոսակցական ձևերը»։</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1) The 3rd-person auxiliary: «ա» instead of «է»: Ի՞նչ ա (What is it?), Լավ ա (Fine), Գնում ա (He is going), Եկել ա (He has come), Պետք ա (Must). In the negative «չի» stays: Չի գալիս. 2) Demonstratives: էս (this), էդ (that, near you), էն (that), էստեղ, էդտեղ, էնտեղ (here, there), էսպես, էդպես/տենց (like this/that), էսքան, էդքան (this/that much), էսօր (today). 3) Questions: ո՞նց (how), ինչի՞ (why), ինչքա՞ն (how much), ու՞ր (where to), ո՞վ ա (who is it). 4) “Can”: կարամ, կարաս, կարա, կարանք, կարաք, կարան; չեմ կարա (I can’t). 5) The imperative of -ել verbs: -ի instead of -իր: նայի, սպասի, գրի, զանգի, խմի, լսի; տու instead of տուր. 6) Colloquial aorist: ասի, ասեց (instead of ասացի, ասաց), տվի (instead of տվեցի). 7) Words: էգուց (tomorrow), էրեկ (yesterday), ձեն (voice), փող (money), գործ (work), սաղ (everyone), մենակ (only), լրիվ (totally), մի հատ (just, a bit). 8) Particles: էլի (come on, please), դե (well), բա (and, so), հը (well?), ախր (after all), հո (surely). 9) Loanwords from Russian: մերսի (from French), նորմալ, պրոբլեմ, մարշրուտկա, պրոբկա, վաբշե. 10) Where to use what: with friends, in a taxi, at the market colloquial forms sound natural; in documents, letters and exams use only literary forms. In the app colloquial words are marked «coll.»; in Settings you can turn on “Colloquial forms first”.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Замените литературные формы разговорными: Ինչպե՞ս ես։ Այսօր չեմ կարող։ Վաղը կզանգեմ։ Սպասիր։</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Գրական ձևերը փոխարինե՛ք խոսակցականով՝ Ինչպե՞ս ես։ Այսօր չեմ կարող։ Վաղը կզանգեմ։ Սպասիր։</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Replace literary forms with colloquial ones: Ինչպե՞ս ես։ Այսօր չեմ կարող։ Վաղը կզանգեմ։ Սպասիր։</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>И наоборот — сделайте литературным: Էս ի՞նչ ա։ Կարամ գամ։ Էգուց կզանգեմ։ Նայի։</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Եվ հակառակը՝ դարձրե՛ք գրական՝ Էս ի՞նչ ա։ Կարամ գամ։ Էգուց կզանգեմ։ Նայի։</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>And vice versa — make literary: Էս ի՞նչ ա։ Կարամ գամ։ Էգուց կզանգեմ։ Նայի։</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Составьте короткий разговор с таксистом (6 реплик) в разговорном стиле.</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Կազմե՛ք կարճ երկխոսություն տաքսու վարորդի հետ (6 արտահայտություն) խոսակցական ոճով։</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Write a short conversation with a taxi driver (6 lines) in colloquial style.</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Выпишите из темы «Разговорная речь» 10 слов, заимствованных из русского или других языков.</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Դուրս գրե՛ք «Խոսակցական լեզու» թեմայից 10 բառ՝ փոխառված ռուսերենից կամ այլ լեզուներից։</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Write out 10 words from the “Spoken” topic borrowed from Russian or other languages.</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Объясните, в каких ситуациях разговорные формы неуместны (3–4 примера).</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Բացատրե՛ք, թե որ իրավիճակներում են խոսակցական ձևերը անտեղի (3–4 օրինակ)։</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Explain in which situations colloquial forms are inappropriate (3–4 examples).</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>Учебники армянского языка; Armenian: An Essential Grammar (Dum-Tragut); Ժամանակակից հայերենի քերականություն</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1" s="10">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Фонетика</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Пунктуация и знаки интонации: ։ ՝ ՞ ՛ ՜ (Կետադրություն)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>В армянском свои знаки препинания: ։ (վերջակետ) — точка в конце предложения; ՝ (բութ) — короткая пауза; ՞ (հարցական նշան) — ставится НАД ударной гласной вопросительного слова: Ինչպե՞ս ես; ՛ (շեշտ) — восклицание или приказ: Արի՛; ՜ (երկարացման նշան) — удивление, растяжка: Ի՜նչ գեղեցիկ է.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Հայերենն ունի իր կետադրական նշանները՝ ։ (վերջակետ), ՝ (բութ), ՞ (հարցական նշան, դրվում է հարցական բառի շեշտված ձայնավորի վրա՝ Ինչպե՞ս ես), ՛ (շեշտ՝ բացականչություն կամ հրաման՝ Արի՛), ՜ (երկարացման նշան՝ Ի՜նչ գեղեցիկ է)։</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Armenian has its own punctuation: ։ (verjaket) — the full stop; ՝ (but) — a short pause; ՞ (question mark) — placed OVER the stressed vowel of the question word: Ինչպե՞ս ես; ՛ (shesht) — exclamation or command: Արի՛; ՜ (lengthening mark) — surprise: Ի՜նչ գեղեցիկ է.</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1) Վերջակետ ։ — главный знак конца предложения (похож на двоеточие): Ես ուսանող եմ։ Обычная точка «.» в армянском используется в сокращениях и датах. 2) Միջակետ ․ (точка на средней линии) — ставится перед пояснением или перечислением, как русское двоеточие: Գնեցի երեք բան․ հաց, պանիր և կաթ. На клавиатуре его часто заменяют обычной точкой или двоеточием. 3) Ստորակետ , — запятая, как в русском. 4) Բութ ՝ — короткая пауза; ставится после обращения или там, где пропущено слово, а также перед пояснением: Արամ՝ իմ ընկերը, բժիշկ է (Арам, мой друг, — врач). Ես՝ Երևան, նա՝ Գյումրի (Я — в Ереван, он — в Гюмри). 5) Հարցական նշան ՞ — ставится над последней гласной ударного слога в слове, на котором держится вопрос: Ո՞վ է, Ե՞րբ ես գալու, Դու՞ ես (Это ты?), Գնացի՞ր. В конце предложения при этом ставится ։. 6) Շեշտ ՛ — над ударной гласной в восклицании, просьбе, приказе: Կանգնի՛ր (Стой!), Լսե՛ք (Послушайте!), Մի՛ արա (Не делай!). 7) Բացականչական նշան ՜ — удивление, восхищение, растягивание: Ա՜խ, Ի՜նչ լավ է, Վա՜յ. 8) Кавычки «…» — ёлочки, как в русском. 9) При поиске и проверке ответов в приложении знаки ՞ ՛ ՜ не учитываются — их можно не набирать.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>1) Վերջակետ ։ — նախադասության վերջի հիմնական նշանը՝ Ես ուսանող եմ։ Սովորական «.» կետը գործածվում է կրճատումներում և ամսաթվերում։ 2) Միջակետ ․ — դրվում է բացատրությունից կամ թվարկումից առաջ՝ Գնեցի երեք բան․ հաց, պանիր և կաթ։ 3) Ստորակետ , — ինչպես ռուսերենում։ 4) Բութ ՝ — կարճ դադար՝ դիմելուց հետո, բաց թողնված բառի տեղում և բացատրությունից առաջ՝ Արամը՝ իմ ընկերը, բժիշկ է։ Ես՝ Երևան, նա՝ Գյումրի։ 5) Հարցական նշան ՞ — դրվում է այն բառի շեշտված վանկի ձայնավորի վրա, որի վրա է հարցը՝ Ո՞վ է, Ե՞րբ ես գալու, Դու՞ ես, Գնացի՞ր։ Նախադասության վերջում դրվում է ։։ 6) Շեշտ ՛ — բացականչության, խնդրանքի, հրամանի մեջ՝ Կանգնի՛ր, Լսե՛ք, Մի՛ արա։ 7) Բացականչական նշան ՜ — զարմանք, հիացմունք՝ Ա՜խ, Ի՜նչ լավ է, Վա՜յ։ 8) Չակերտներ «…»։ 9) Հավելվածում պատասխանները ստուգելիս ՞ ՛ ՜ նշանները հաշվի չեն առնվում՝ կարելի է չհավաքել։</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1) Verjaket ։ — the main sentence-final mark (it looks like a colon): Ես ուսանող եմ։ The ordinary dot «.» is used in abbreviations and dates. 2) Mijaket ․ (a raised dot) — before an explanation or a list, like a colon: Գնեցի երեք բան․ հաց, պանիր և կաթ. On keyboards it is often replaced by a dot or a colon. 3) Storaket , — the comma, as in English. 4) But ՝ — a short pause: after an address, in place of an omitted word, and before an explanation: Արամը՝ իմ ընկերը, բժիշկ է (Aram, my friend, is a doctor). Ես՝ Երևան, նա՝ Գյումրի (I — to Yerevan, he — to Gyumri). 5) The question mark ՞ — placed over the vowel of the stressed syllable of the word carrying the question: Ո՞վ է, Ե՞րբ ես գալու, Դու՞ ես (Is it you?), Գնացի՞ր. The sentence still ends with ։. 6) Shesht ՛ — over the stressed vowel in exclamations, requests and commands: Կանգնի՛ր (Stop!), Լսե՛ք (Listen!), Մի՛ արա (Don’t!). 7) The exclamation mark ՜ — surprise, admiration: Ա՜խ, Ի՜նչ լավ է, Վա՜յ. 8) Quotation marks «…». 9) The app ignores ՞ ՛ ՜ when checking answers — you may skip them.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Расставьте знаки препинания: Ինչպես ես / Արի այստեղ / Ինչ գեղեցիկ է / Ես ուսանող եմ</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Դրե՛ք կետադրական նշանները՝ Ինչպես ես / Արի այստեղ / Ինչ գեղեցիկ է / Ես ուսանող եմ</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Add punctuation: Ինչպես ես / Արի այստեղ / Ինչ գեղեցիկ է / Ես ուսանող եմ</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Поставьте ՞ над нужной гласной: Ով է, Երբ ես գալու, Որտեղ ես ապրում, Դու ես.</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Դրե՛ք ՞ նշանը ճիշտ ձայնավորի վրա՝ Ով է, Երբ ես գալու, Որտեղ ես ապրում, Դու ես։</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Put ՞ over the right vowel: Ով է, Երբ ես գալու, Որտեղ ես ապրում, Դու ես.</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Объясните, чем отличаются вопросы: Դու՞ ես գնալու։ / Դու գնալո՞ւ ես։</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Բացատրե՛ք հարցերի տարբերությունը՝ Դու՞ ես գնալու։ / Դու գնալո՞ւ ես։</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Explain the difference: Դու՞ ես գնալու։ / Դու գնալո՞ւ ես։</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Напишите 3 приказа со знаком ՛ и 2 восклицания со знаком ՜.</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Գրե՛ք 3 հրաման ՛ նշանով և 2 բացականչություն ՜ նշանով։</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Write 3 commands with ՛ and 2 exclamations with ՜.</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Найдите в любом армянском тексте все знаки ։ ՝ ՞ ՛ и объясните их.</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ցանկացած հայերեն տեքստում գտե՛ք ։ ՝ ՞ ՛ նշանները և բացատրե՛ք դրանք։</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Find all ։ ՝ ՞ ՛ marks in any Armenian text and explain them.</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>Учебники армянского языка; Armenian: An Essential Grammar (Dum-Tragut); Ժամանակակից հայերենի քերականություն</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="15.75" customHeight="1" s="10">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Живой язык</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Восточный и западный армянский (Արևելահայերեն և արևմտահայերեն)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Армянский существует в двух литературных вариантах: восточный (Армения, Иран, Россия) — его изучаете вы, и западный (диаспора: Ливан, Сирия, Франция, США). Они понятны друг другу, но различаются произношением согласных, формами глагола и орфографией.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Հայերենն ունի երկու գրական տարբերակ՝ արևելահայերեն (Հայաստան, Իրան, Ռուսաստան), որը դուք սովորում եք, և արևմտահայերեն (սփյուռք՝ Լիբանան, Սիրիա, Ֆրանսիա, ԱՄՆ)։ Դրանք փոխըմբռնելի են, բայց տարբերվում են բաղաձայնների արտասանությամբ, բայաձևերով և ուղղագրությամբ։</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Armenian has two literary standards: Eastern (Armenia, Iran, Russia), which you are learning, and Western (the diaspora: Lebanon, Syria, France, the USA). They are mutually intelligible but differ in the pronunciation of consonants, verb forms and spelling.</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1) История: после событий начала XX века западноармянские общины оказались в диаспоре; восточный армянский стал государственным языком Армении. 2) Произношение: в западном армянском звонкие и глухие согласные «меняются местами»: բ звучит как [п], պ — как [б]; դ — [т], տ — [д]; գ — [к], կ — [г]; ձ — [ц], ծ — [дз]; ջ — [ч], ճ — [дж]. Поэтому имя Պետրոս на Западе звучит «Бедрос», а слово բարև — «парев». 3) Глагол: настоящее время на Востоке — գրում եմ, на Западе — կը գրեմ (կը + желательная форма); будущее: Восток գրելու եմ / կգրեմ, Запад — պիտի գրեմ. Отрицание на Западе: չեմ գրեր. Глаголы на -իլ: Восток խոսել — Запад խօսիլ. 4) Местоимения и слова: Восток նա (он) — Запад ան; այս/այդ/այն — Запад ասիկա/ատիկա/անիկա; «хорошо» Восток լավ — Запад լաւ. 5) Орфография: Армения с 1922–1940 гг. пользуется реформированной орфографией (յուղ, լավ, ով), диаспора и западный армянский — классической, «маштоцевской» (իւղ, լաւ, ո՞վ с другими буквами: իւ, աւ, օ). 6) Восточный армянский в Иране сохраняет классическую орфографию. 7) Что знать вам: если вы слышите «կը» перед глаголом и «оглушённые» согласные — это западный армянский; понимать его можно, но писать и говорить лучше на восточном, как в этом приложении.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>1) Պատմություն՝ XX դարի սկզբի իրադարձություններից հետո արևմտահայ համայնքները հայտնվեցին սփյուռքում, իսկ արևելահայերենը դարձավ Հայաստանի պետական լեզուն։ 2) Արտասանություն՝ արևմտահայերենում ձայնեղ և խուլ բաղաձայնները «տեղերով փոխվում են»՝ բ-ն հնչում է [պ], պ-ն՝ [բ], դ՝ [տ], տ՝ [դ], գ՝ [կ], կ՝ [գ], ձ՝ [ց], ծ՝ [ձ], ջ՝ [չ], ճ՝ [ջ]։ Այդ պատճառով Պետրոս անունը Արևմուտքում հնչում է «Բեդրոս», իսկ բարև-ը՝ «պարև»։ 3) Բայ՝ ներկան Արևելքում՝ գրում եմ, Արևմուտքում՝ կը գրեմ, ապառնին՝ Արևելքում գրելու եմ / կգրեմ, Արևմուտքում՝ պիտի գրեմ։ Ժխտականը Արևմուտքում՝ չեմ գրեր։ -իլ բայեր՝ խոսել — խօսիլ։ 4) Դերանուններ և բառեր՝ նա — ան, այս/այդ/այն — ասիկա/ատիկա/անիկա, լավ — լաւ։ 5) Ուղղագրություն՝ Հայաստանը 1922–1940 թթ.-ից գործածում է բարեփոխված ուղղագրությունը (յուղ, լավ), սփյուռքը և արևմտահայերենը՝ դասական, մաշտոցյան ուղղագրությունը (իւղ, լաւ)։ 6) Իրանի արևելահայերը պահպանում են դասական ուղղագրությունը։ 7) Ինչ իմանալ՝ եթե լսում եք «կը» բայից առաջ և «շրջված» բաղաձայններ, դա արևմտահայերեն է. այն կարելի է հասկանալ, բայց գրել և խոսել ավելի լավ է արևելահայերենով, ինչպես այս հավելվածում։</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1) History: after the events of the early 20th century the Western Armenian communities ended up in the diaspora, while Eastern Armenian became the state language of Armenia. 2) Pronunciation: in Western Armenian voiced and voiceless consonants “swap places”: բ sounds like [p], պ like [b]; դ — [t], տ — [d]; գ — [k], կ — [g]; ձ — [ts], ծ — [dz]; ջ — [ch], ճ — [j]. So the name Պետրոս sounds “Bedros” in the West, and բարև — “parev”. 3) The verb: the present in the East is գրում եմ, in the West կը գրեմ (կը + subjunctive); the future: East գրելու եմ / կգրեմ, West պիտի գրեմ. The Western negative: չեմ գրեր. Verbs in -իլ: East խոսել — West խօսիլ. 4) Pronouns and words: East նա (he) — West ան; այս/այդ/այն — West ասիկա/ատիկա/անիկա; “good” East լավ — West լաւ. 5) Spelling: Armenia has used the reformed spelling since 1922–1940 (յուղ, լավ), while the diaspora and Western Armenian keep the classical “Mashtotsian” spelling (իւղ, լաւ). 6) Eastern Armenians in Iran also keep the classical spelling. 7) What you need: if you hear «կը» before a verb and “swapped” consonants, it is Western Armenian — you can understand it, but write and speak Eastern Armenian, as in this app.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Прочитайте по-западноармянски (с «обменом» согласных): Պետրոս, բարև, դուռ, կով, ջուր.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Կարդացե՛ք արևմտահայերեն արտասանությամբ՝ Պետրոս, բարև, դուռ, կով, ջուր։</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Read with Western Armenian pronunciation: Պետրոս, բարև, դուռ, կով, ջուր.</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Переведите на восточный армянский: Ես կը գրեմ։ Ան պիտի գայ։ Չեմ գիտեր։</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Թարգմանե՛ք արևելահայերեն՝ Ես կը գրեմ։ Ան պիտի գայ։ Չեմ գիտեր։</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Translate into Eastern Armenian: Ես կը գրեմ։ Ան պիտի գայ։ Չեմ գիտեր։</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Назовите 3 страны, где говорят на восточном армянском, и 3 — где на западном.</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Նշե՛ք 3 երկիր, որտեղ խոսում են արևելահայերեն, և 3՝ որտեղ արևմտահայերեն։</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Name 3 countries where Eastern Armenian is spoken and 3 where Western Armenian is spoken.</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Сравните написание: լավ — լաւ, յուղ — իւղ. Объясните, откуда разница.</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Համեմատե՛ք գրությունը՝ լավ — լաւ, յուղ — իւղ։ Բացատրե՛ք տարբերության պատճառը։</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Compare the spelling: լավ — լաւ, յուղ — իւղ. Explain where the difference comes from.</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Найдите песню на западном армянском и выпишите 5 отличий от восточного.</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Գտե՛ք արևմտահայերեն երգ և դուրս գրե՛ք արևելահայերենից 5 տարբերություն։</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Find a song in Western Armenian and write out 5 differences from Eastern Armenian.</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>Учебники армянского языка; Armenian: An Essential Grammar (Dum-Tragut); Ժամանակակից հայերենի քերականություն</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="15.75" customHeight="1" s="10">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Морфология: имя</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Время, даты и возраст (Ժամ, ամսաթիվ, տարիք)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Который час? — Ժամը քանի՞սն է։ — Ժամը հինգն է (Пять часов). Во сколько? — Ժամը քանիսի՞ն։ — Ժամը վեցին (В шесть). Дата: Այսօր մայիսի 9-ն է. Возраст: Քանի՞ տարեկան ես։ — Քսան տարեկան եմ (Мне двадцать лет).</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Ժամը քանի՞սն է։ — Ժամը հինգն է։ Ժամը քանիսի՞ն։ — Ժամը վեցին։ Ամսաթիվ՝ Այսօր մայիսի 9-ն է։ Տարիք՝ Քանի՞ տարեկան ես։ — Քսան տարեկան եմ։</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>What time is it? — Ժամը քանի՞սն է։ — Ժամը հինգն է (It is five). At what time? — Ժամը քանիսի՞ն։ — Ժամը վեցին (At six). The date: Այսօր մայիսի 9-ն է. Age: Քանի՞ տարեկան ես։ — Քսան տարեկան եմ (I am twenty).</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1) Время: Ժամը քանի՞սն է (Который час?) — Ժամը երեքն է (Три часа). Минуты: Ժամը երեքն անց տասը (Десять минут четвёртого, букв. «три и десять сверху»), Ժամը երեքն անց կես / Ժամը երեքուկես (Половина четвёртого), Ժամը չորսին տասը պակաս (Без десяти четыре), Ժամը երեքն անց քառորդ (Четверть четвёртого). В официальной речи — 24 часа: ժամը 18:30 (տասնութն անց երեսուն). 2) «Во сколько?» — дательный падеж: Ժամը քանիսի՞ն (Во сколько?) — Ժամը յոթին (В семь), Ժամը իննին (В девять). Части дня: առավոտյան (утром), ցերեկը (днём), երեկոյան (вечером), գիշերը (ночью): առավոտյան ժամը ութին (в восемь утра). 3) Дни недели: երկուշաբթի, երեքշաբթի, չորեքշաբթի, հինգշաբթի, ուրբաթ, շաբաթ, կիրակի; «в понедельник» — երկուշաբթի օրը. 4) Даты: месяц в родительном падеже + число: մայիսի 28 (28 мая) — читается մայիսի քսանութ; Այսօր ապրիլի 24-ն է (Сегодня 24 апреля). Год: 2026 թվական(ին) — «в 2026 году»: 1991 թվականին. Сокращение: 2026 թ. 5) Возраст: Քանի՞ տարեկան ես (Сколько тебе лет?) — Երեսուն տարեկան եմ. О ребёнке: Երեք ամսական է (Ему три месяца). 6) Длительность: երկու ժամ (два часа), կես ժամ (полчаса), մեկ ու կես ժամ (полтора часа); «через» — հետո: մի ժամից (через час), երկու օրից; «назад» — առաջ: երեք օր առաջ.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>1) Ժամ՝ Ժամը քանի՞սն է — Ժամը երեքն է։ Րոպեներ՝ Ժամը երեքն անց տասը, Ժամը երեքն անց կես / Ժամը երեքուկես, Ժամը չորսին տասը պակաս, Ժամը երեքն անց քառորդ։ Պաշտոնական խոսքում՝ 24 ժամ՝ ժամը 18:30 (տասնութն անց երեսուն)։ 2) «Ո՞ր ժամին» — տրական հոլով՝ Ժամը քանիսի՞ն — Ժամը յոթին, Ժամը իննին։ Օրվա մասեր՝ առավոտյան, ցերեկը, երեկոյան, գիշերը՝ առավոտյան ժամը ութին։ 3) Շաբաթվա օրեր՝ երկուշաբթի, երեքշաբթի, չորեքշաբթի, հինգշաբթի, ուրբաթ, շաբաթ, կիրակի, «երկուշաբթի» — երկուշաբթի օրը։ 4) Ամսաթիվ՝ ամիսը սեռական հոլովով + թիվը՝ մայիսի 28 (կարդացվում է մայիսի քսանութ)։ Այսօր ապրիլի 24-ն է։ Տարի՝ 2026 թվական(ին)՝ 1991 թվականին։ Կրճատ՝ 2026 թ.։ 5) Տարիք՝ Քանի՞ տարեկան ես — Երեսուն տարեկան եմ։ Երեխայի մասին՝ Երեք ամսական է։ 6) Տևողություն՝ երկու ժամ, կես ժամ, մեկ ու կես ժամ, «… հետո»՝ մի ժամից, երկու օրից, «… առաջ»՝ երեք օր առաջ։</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1) The time: Ժամը քանի՞սն է (What time is it?) — Ժամը երեքն է (It is three). Minutes: Ժամը երեքն անց տասը (Ten past three, lit. “three and ten over”), Ժամը երեքն անց կես / Ժամը երեքուկես (Half past three), Ժամը չորսին տասը պակաս (Ten to four), Ժամը երեքն անց քառորդ (Quarter past three). Official speech uses the 24-hour clock: ժամը 18:30 (տասնութն անց երեսուն). 2) “At what time?” uses the dative: Ժամը քանիսի՞ն (At what time?) — Ժամը յոթին (At seven), Ժամը իննին (At nine). Parts of the day: առավոտյան (in the morning), ցերեկը (in the afternoon), երեկոյան (in the evening), գիշերը (at night): առավոտյան ժամը ութին (at 8 a.m.). 3) Days of the week: երկուշաբթի, երեքշաբթի, չորեքշաբթի, հինգշաբթի, ուրբաթ, շաբաթ, կիրակի; “on Monday” — երկուշաբթի օրը. 4) Dates: the month in the genitive + the number: մայիսի 28 (28 May), read մայիսի քսանութ; Այսօր ապրիլի 24-ն է (Today is 24 April). The year: 2026 թվական(ին) — “in 2026”: 1991 թվականին. Abbreviation: 2026 թ. 5) Age: Քանի՞ տարեկան ես (How old are you?) — Երեսուն տարեկան եմ (I am thirty). About a baby: Երեք ամսական է (He is three months old). 6) Duration: երկու ժամ (two hours), կես ժամ (half an hour), մեկ ու կես ժամ (an hour and a half); “in” — մի ժամից (in an hour), երկու օրից (in two days); “ago” — երեք օր առաջ (three days ago).</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Скажите по-армянски время: 7:00, 9:15, 12:30, 18:45, 22:10.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Ասե՛ք հայերեն ժամը՝ 7:00, 9:15, 12:30, 18:45, 22:10։</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Say the time in Armenian: 7:00, 9:15, 12:30, 18:45, 22:10.</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Ответьте на вопросы: Ժամը քանիսի՞ն ես արթնանում։ Ե՞րբ է ծննդյանդ օրը։ Քանի՞ տարեկան ես։</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Պատասխանե՛ք՝ Ժամը քանիսի՞ն ես արթնանում։ Ե՞րբ է ծննդյանդ օրը։ Քանի՞ տարեկան ես։</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Answer: Ժամը քանիսի՞ն ես արթնանում։ Ե՞րբ է ծննդյանդ օրը։ Քանի՞ տարեկան ես։</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Запишите словами даты: 1 января, 28 мая 1918 года, 21 сентября 1991 года.</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Բառերով գրե՛ք ամսաթվերը՝ հունվարի 1, 1918 թ. մայիսի 28, 1991 թ. սեպտեմբերի 21։</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Write the dates in words: 1 January, 28 May 1918, 21 September 1991.</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Составьте свой распорядок дня с указанием времени (6 предложений).</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Կազմե՛ք ձեր օրվա ռեժիմը՝ նշելով ժամերը (6 նախադասություն)։</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Write your daily routine with times (6 sentences).</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Переведите: «через час», «три дня назад», «в пятницу вечером», «полтора часа».</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Թարգմանե՛ք՝ «через час», «три дня назад», «в пятницу вечером», «полтора часа»։</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Translate: “in an hour”, “three days ago”, “on Friday evening”, “an hour and a half”.</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>Учебники армянского языка; Armenian: An Essential Grammar (Dum-Tragut); Ժամանակակից հայերենի քերականություն</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="15.75" customHeight="1" s="10">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Морфология: имя</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Словообразование: −ություն, −ական, −ուհի, −իչ, −արան, −անոց (Բառակազմություն)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Армянский легко строит слова из корней и суффиксов. -ություն — отвлечённое существительное (ազատ → ազատություն — свобода); -ական — прилагательное (պետություն → պետական); -ուհի — женский род профессии (ուսուցիչ → ուսուցչուհի); -իչ — деятель или прибор (ուսուցիչ — учитель, հաշվել → հաշվիչ — счётчик); -արան/-անոց — место (գրադարան, հիվանդանոց).</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Հայերենը հեշտությամբ բառեր է կազմում արմատներից և ածանցներից՝ -ություն (ազատ → ազատություն), -ական (պետություն → պետական), -ուհի (ուսուցիչ → ուսուցչուհի), -իչ (հաշվել → հաշվիչ), -արան/-անոց (գրադարան, հիվանդանոց)։</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Armenian builds words easily from roots and suffixes. -ություն forms abstract nouns (ազատ → ազատություն freedom); -ական forms adjectives (պետություն → պետական); -ուհի forms the feminine of professions (ուսուցիչ → ուսուցչուհի); -իչ — a doer or a device (հաշվել → հաշվիչ counter); -արան/-անոց — a place (գրադարան library, հիվանդանոց hospital).</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1) Суффиксы существительных: -ություն — отвлечённое понятие: ազատ (свободный) → ազատություն (свобода), բարի (добрый) → բարություն (доброта), երջանիկ → երջանկություն (счастье), ընկեր → ընկերություն (дружба; компания). -ում — действие: զարգանալ → զարգացում (развитие), որոշել → որոշում (решение). -իչ — деятель или прибор: ուսուցիչ (учитель), վարիչ (заведующий), հաշվիչ (счётчик), համակարգիչ (компьютер). -ող — тот, кто делает: ուսանող, վարող. -որդ — профессия: վարորդ (водитель), որսորդ (охотник). -ուհի — женщина: ուսուցչուհի (учительница), դերասանուհի (актриса), ընկերուհի (подруга). 2) Место: -արան: գրադարան (библиотека, от գիր — письмо, книга), ճաշարան (столовая), համալսարան (университет); -անոց: հիվանդանոց (больница), հյուրանոց (гостиница), մանկանոց (ясли); -ատուն: դեղատուն (аптека). 3) Прилагательные: -ական: պետություն → պետական (государственный), Հայաստան → հայկական (армянский), պատմություն → պատմական (исторический); -ային: ծով → ծովային (морской), լեռ → լեռնային (горный). Отрицание: ան- (անհամ — безвкусный, անհաջող — неудачный), դժ- (դժբախտ — несчастный). 4) Сложные слова через -ա-: դաս + գիրք → դասագիրք (учебник), քաղաք + ապետ → քաղաքապետ (мэр), հեռու + խոս → հեռախոս (телефон), երկաթ + ուղի → երկաթուղի (железная дорога). 5) Зная 20–30 суффиксов и корней, вы будете догадываться о значении сотен новых слов.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>1) Գոյականակերտ ածանցներ՝ -ություն՝ վերացական գոյական՝ ազատ → ազատություն, բարի → բարություն, երջանիկ → երջանկություն, ընկեր → ընկերություն։ -ում՝ գործողություն՝ զարգանալ → զարգացում, որոշել → որոշում։ -իչ՝ կատարող կամ սարք՝ ուսուցիչ, վարիչ, հաշվիչ, համակարգիչ։ -ող՝ ուսանող, վարող։ -որդ՝ մասնագիտություն՝ վարորդ, որսորդ։ -ուհի՝ իգական՝ ուսուցչուհի, դերասանուհի, ընկերուհի։ 2) Տեղ՝ -արան՝ գրադարան, ճաշարան, համալսարան, -անոց՝ հիվանդանոց, հյուրանոց, մանկանոց, -ատուն՝ դեղատուն։ 3) Ածականակերտ ածանցներ՝ -ական՝ պետական, հայկական, պատմական, -ային՝ ծովային, լեռնային։ Ժխտական նախածանցներ՝ ան- (անհամ, անհաջող), դժ- (դժբախտ)։ 4) Բարդ բառեր -ա- հոդակապով՝ դաս + գիրք → դասագիրք, քաղաք + ապետ → քաղաքապետ, հեռու + խոս → հեռախոս, երկաթ + ուղի → երկաթուղի։ 5) Իմանալով 20–30 ածանց և արմատ՝ կկարողանաք կռահել հարյուրավոր նոր բառերի իմաստը։</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1) Noun suffixes: -ություն — abstract nouns: ազատ (free) → ազատություն (freedom), բարի (kind) → բարություն (kindness), երջանիկ → երջանկություն (happiness), ընկեր → ընկերություն (friendship; company). -ում — an action: զարգանալ → զարգացում (development), որոշել → որոշում (decision). -իչ — a doer or a device: ուսուցիչ (teacher), վարիչ (manager), հաշվիչ (counter), համակարգիչ (computer). -ող — one who does: ուսանող, վարող. -որդ — an occupation: վարորդ (driver), որսորդ (hunter). -ուհի — a woman: ուսուցչուհի (female teacher), դերասանուհի (actress), ընկերուհի (girlfriend). 2) Places: -արան: գրադարան (library), ճաշարան (canteen), համալսարան (university); -անոց: հիվանդանոց (hospital), հյուրանոց (hotel), մանկանոց (nursery); -ատուն: դեղատուն (pharmacy). 3) Adjective suffixes: -ական: պետական (state), հայկական (Armenian), պատմական (historical); -ային: ծովային (sea), լեռնային (mountain). Negative prefixes: ան- (անհամ — tasteless, անհաջող — unsuccessful), դժ- (դժբախտ — unhappy). 4) Compounds with the linking vowel -ա-: դաս + գիրք → դասագիրք (textbook), քաղաք + ապետ → քաղաքապետ (mayor), հեռու + խոս → հեռախոս (telephone), երկաթ + ուղի → երկաթուղի (railway). 5) Knowing 20–30 suffixes and roots, you will be able to guess hundreds of new words.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Образуйте существительные на -ություն: ազատ, բարի, երջանիկ, գեղեցիկ, ընկեր.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Կազմե՛ք -ություն գոյականներ՝ ազատ, բարի, երջանիկ, գեղեցիկ, ընկեր։</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Form -ություն nouns from ազատ, բարի, երջանիկ, գեղեցիկ, ընկեր.</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Образуйте прилагательные на -ական/-ային: պետություն, պատմություն, ծով, լեռ, Հայաստան.</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Կազմե՛ք -ական/-ային ածականներ՝ պետություն, պատմություն, ծով, լեռ, Հայաստան։</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Form -ական/-ային adjectives from պետություն, պատմություն, ծով, լեռ, Հայաստան.</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Разберите по составу: դասագիրք, հեռախոս, հիվանդանոց, ուսուցչուհի, անհաջող.</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Կազմությամբ վերլուծե՛ք՝ դասագիրք, հեռախոս, հիվանդանոց, ուսուցչուհի, անհաջող։</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Analyse the structure: դասագիրք, հեռախոս, հիվանդանոց, ուսուցչուհի, անհաջող.</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Назовите женский вариант: ուսուցիչ, դերասան, ընկեր, երգիչ, բժիշկ (если есть).</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Ասե՛ք իգական տարբերակը՝ ուսուցիչ, դերասան, ընկեր, երգիչ, բժիշկ (եթե կա)։</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Give the feminine form: ուսուցիչ, դերասան, ընկեր, երգիչ, բժիշկ (if it exists).</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Найдите в словаре 10 слов с суффиксами -արան или -անոց и угадайте их значение до перевода.</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Բառարանում գտե՛ք -արան կամ -անոց ածանցով 10 բառ և գուշակե՛ք իմաստը մինչև թարգմանությունը։</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Find 10 words with -արան or -անոց in the dictionary and guess their meaning before checking.</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>Учебники армянского языка; Armenian: An Essential Grammar (Dum-Tragut); Ժամանակակից հայերենի քերականություն</t>
+        </is>
+      </c>
+    </row>
     <row r="38" ht="15.75" customHeight="1" s="10"/>
     <row r="39" ht="15.75" customHeight="1" s="10"/>
     <row r="40" ht="15.75" customHeight="1" s="10"/>
